--- a/livrables/marges_2x2_synthese.xlsx
+++ b/livrables/marges_2x2_synthese.xlsx
@@ -503,19 +503,19 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="E2" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="F2" t="n">
-        <v>44.3</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="H2" t="n">
-        <v>69.8</v>
+        <v>97</v>
       </c>
       <c r="I2" t="n">
         <v>5</v>
@@ -536,19 +536,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>65.2</v>
+        <v>67.8</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>67.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>60.8</v>
+        <v>62.1</v>
       </c>
       <c r="H3" t="n">
-        <v>69.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>21.4</v>
@@ -569,19 +569,19 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>33.8</v>
       </c>
       <c r="E4" t="n">
-        <v>33.2</v>
+        <v>20.6</v>
       </c>
       <c r="F4" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>18.4</v>
       </c>
       <c r="H4" t="n">
-        <v>62.5</v>
+        <v>65.5</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -602,19 +602,19 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>75.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>101.8</v>
+        <v>102.1</v>
       </c>
       <c r="G5" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>114.1</v>
+        <v>113</v>
       </c>
       <c r="I5" t="n">
         <v>7.1</v>
@@ -635,19 +635,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>258.6</v>
+        <v>233.7</v>
       </c>
       <c r="E6" t="n">
-        <v>215.3</v>
+        <v>205</v>
       </c>
       <c r="F6" t="n">
-        <v>258.8</v>
+        <v>248.2</v>
       </c>
       <c r="G6" t="n">
-        <v>172</v>
+        <v>176.3</v>
       </c>
       <c r="H6" t="n">
-        <v>259</v>
+        <v>262.7</v>
       </c>
     </row>
     <row r="7">
@@ -665,19 +665,19 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>124.8</v>
+        <v>125</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>104.7</v>
       </c>
       <c r="F7" t="n">
-        <v>145.5</v>
+        <v>145.4</v>
       </c>
       <c r="G7" t="n">
-        <v>83.2</v>
+        <v>84.3</v>
       </c>
       <c r="H7" t="n">
-        <v>166.3</v>
+        <v>165.8</v>
       </c>
     </row>
     <row r="8">
@@ -695,19 +695,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>68.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>68.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>68.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>68.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>68.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>15.7</v>

--- a/livrables/marges_2x2_synthese.xlsx
+++ b/livrables/marges_2x2_synthese.xlsx
@@ -503,19 +503,19 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>36.6</v>
+        <v>32.6</v>
       </c>
       <c r="E2" t="n">
-        <v>34.1</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>32.4</v>
+        <v>24.8</v>
       </c>
       <c r="H2" t="n">
-        <v>97</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
         <v>5</v>
@@ -536,19 +536,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>67.8</v>
+        <v>59.8</v>
       </c>
       <c r="E3" t="n">
-        <v>64.90000000000001</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>70.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="G3" t="n">
-        <v>62.1</v>
+        <v>54.2</v>
       </c>
       <c r="H3" t="n">
-        <v>73.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>21.4</v>
@@ -569,19 +569,19 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>33.8</v>
+        <v>28.6</v>
       </c>
       <c r="E4" t="n">
-        <v>20.6</v>
+        <v>16.1</v>
       </c>
       <c r="F4" t="n">
-        <v>51.2</v>
+        <v>46.9</v>
       </c>
       <c r="G4" t="n">
-        <v>18.4</v>
+        <v>13.4</v>
       </c>
       <c r="H4" t="n">
-        <v>65.5</v>
+        <v>60.7</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -602,19 +602,19 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>85.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>79.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="F5" t="n">
-        <v>102.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>67.09999999999999</v>
+        <v>59.2</v>
       </c>
       <c r="H5" t="n">
-        <v>113</v>
+        <v>107.7</v>
       </c>
       <c r="I5" t="n">
         <v>7.1</v>
@@ -635,19 +635,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>233.7</v>
+        <v>224.3</v>
       </c>
       <c r="E6" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F6" t="n">
-        <v>248.2</v>
+        <v>236.2</v>
       </c>
       <c r="G6" t="n">
-        <v>176.3</v>
+        <v>169.6</v>
       </c>
       <c r="H6" t="n">
-        <v>262.7</v>
+        <v>248.1</v>
       </c>
     </row>
     <row r="7">
@@ -665,19 +665,19 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>115.7</v>
       </c>
       <c r="E7" t="n">
-        <v>104.7</v>
+        <v>92.7</v>
       </c>
       <c r="F7" t="n">
-        <v>145.4</v>
+        <v>138.7</v>
       </c>
       <c r="G7" t="n">
-        <v>84.3</v>
+        <v>69.7</v>
       </c>
       <c r="H7" t="n">
-        <v>165.8</v>
+        <v>161.7</v>
       </c>
     </row>
     <row r="8">
